--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488157_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488157_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8515</v>
+        <v>5.1212</v>
       </c>
       <c r="E2" t="n">
-        <v>5.405</v>
+        <v>5.6009</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5536</v>
+        <v>-0.4797</v>
       </c>
       <c r="G2" t="n">
         <v>6.1485</v>
@@ -610,13 +610,13 @@
         <v>2.2234</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8349</v>
+        <v>-0.5652</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0396</v>
+        <v>-0.8437</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2047</v>
+        <v>0.2785</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5738</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.71</v>
+        <v>1.269</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1929</v>
+        <v>1.8012</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.483</v>
+        <v>-0.5322</v>
       </c>
       <c r="G3" t="n">
         <v>1.6669</v>
@@ -688,13 +688,13 @@
         <v>0.7411</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2283</v>
+        <v>-0.2126</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3793</v>
+        <v>-0.0124</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.151</v>
+        <v>-0.2002</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3298</v>
+        <v>-1.355</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4565</v>
+        <v>-0.3585</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8733</v>
+        <v>-0.9964</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4472</v>
@@ -922,13 +922,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0062</v>
+        <v>-0.019</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3345</v>
+        <v>0.2114</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2594</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5241</v>
+        <v>-2.5492</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1708</v>
+        <v>1.2688</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.6949</v>
+        <v>-3.818</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2517</v>
@@ -1000,13 +1000,13 @@
         <v>1.1117</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8108</v>
+        <v>-0.836</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4924</v>
+        <v>-0.3945</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3184</v>
+        <v>-0.4415</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5733</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6951</v>
+        <v>-3.5725</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8329</v>
+        <v>-0.7349</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8622</v>
+        <v>-2.8376</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4365</v>
@@ -1078,13 +1078,13 @@
         <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3142</v>
+        <v>-1.1916</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0943</v>
+        <v>-0.9964</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2199</v>
+        <v>-0.1952</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9444</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MALINIC</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7111</v>
+        <v>-3.9401</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2612</v>
+        <v>-1.733</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4498</v>
+        <v>-2.2072</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0052</v>
+        <v>-4.0787</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0236</v>
+        <v>-3.0234</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0185</v>
+        <v>-1.0553</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0165</v>
+        <v>-0.4129</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7985</v>
+        <v>-1.7613</v>
       </c>
       <c r="L9" t="n">
-        <v>0.218</v>
+        <v>1.3484</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0217</v>
+        <v>-3.6658</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8221</v>
+        <v>-1.2621</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1996</v>
+        <v>-2.4037</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8529</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.891</v>
+        <v>-2.0382</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2236</v>
+        <v>-1.2494</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3867</v>
+        <v>-0.8552</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1631</v>
+        <v>-0.3942</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6294</v>
+        <v>1.5733</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>M. MALINIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3816</v>
+        <v>-4.1285</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0267</v>
+        <v>-3.4571</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3549</v>
+        <v>-0.6714</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.0787</v>
+        <v>-1.0052</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.0234</v>
+        <v>-1.0236</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0553</v>
+        <v>0.0185</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4129</v>
+        <v>1.0165</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7613</v>
+        <v>0.7985</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3484</v>
+        <v>0.218</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.6658</v>
+        <v>-2.0217</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2621</v>
+        <v>-1.8221</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4037</v>
+        <v>-0.1996</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1853</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0382</v>
+        <v>-3.891</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.691</v>
+        <v>-0.641</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.149</v>
+        <v>-0.5826</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5419</v>
+        <v>-0.0585</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5733</v>
+        <v>-0.6294</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.793</v>
+        <v>-4.4981</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1138</v>
+        <v>0.2117</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.9068</v>
+        <v>-4.7098</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8935999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.494</v>
+        <v>-1.1991</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7113</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7827</v>
+        <v>-0.5857</v>
       </c>
       <c r="V11" t="n">
         <v>-3.1466</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2068</v>
+        <v>-7.4267</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.948</v>
+        <v>-4.2417</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2588</v>
+        <v>-3.185</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3572</v>
@@ -1390,13 +1390,13 @@
         <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5526</v>
+        <v>-0.7725</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4961</v>
+        <v>-0.7899</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0565</v>
+        <v>0.0174</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2589</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.486</v>
+        <v>-20.4859</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8663</v>
+        <v>-1.866100000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-18.6198</v>
@@ -1468,13 +1468,13 @@
         <v>14.823</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.9266</v>
+        <v>-6.9264</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.701400000000001</v>
+        <v>-5.7015</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2251</v>
+        <v>-1.225</v>
       </c>
       <c r="V13" t="n">
         <v>-8.8125</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.2925</v>
+        <v>8.5869</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6475</v>
+        <v>6.8434</v>
       </c>
       <c r="F14" t="n">
-        <v>1.645</v>
+        <v>1.7435</v>
       </c>
       <c r="G14" t="n">
         <v>6.6172</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5457</v>
+        <v>0.84</v>
       </c>
       <c r="T14" t="n">
-        <v>0.051</v>
+        <v>0.2469</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4947</v>
+        <v>0.5931</v>
       </c>
       <c r="V14" t="n">
         <v>0.9444</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.3947</v>
+        <v>7.196</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1302</v>
+        <v>4.424</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2645</v>
+        <v>2.772</v>
       </c>
       <c r="G15" t="n">
         <v>0.9688</v>
@@ -1624,13 +1624,13 @@
         <v>2.0382</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5196</v>
+        <v>1.3209</v>
       </c>
       <c r="T15" t="n">
-        <v>0.051</v>
+        <v>0.3448</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4686</v>
+        <v>0.9762</v>
       </c>
       <c r="V15" t="n">
         <v>4.721</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.7771</v>
+        <v>6.6797</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6264</v>
+        <v>4.4305</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1507</v>
+        <v>2.2492</v>
       </c>
       <c r="G16" t="n">
         <v>6.2664</v>
@@ -1702,13 +1702,13 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5668</v>
+        <v>0.4694</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2151</v>
+        <v>0.0193</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3517</v>
+        <v>0.4501</v>
       </c>
       <c r="V16" t="n">
         <v>0.3144</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3816</v>
+        <v>2.8545</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2728</v>
+        <v>2.8545</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1088</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8227</v>
+        <v>2.8545</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5261</v>
+        <v>1.6103</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7034</v>
+        <v>1.2441</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1671</v>
+        <v>2.8545</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1257</v>
+        <v>1.6103</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0415</v>
+        <v>1.2441</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3444</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4004</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7448</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5589</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0321</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5266999999999999</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8545</v>
+        <v>2.8427</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8545</v>
+        <v>1.7832</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.0595</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8545</v>
+        <v>1.8227</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6103</v>
+        <v>2.5261</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2441</v>
+        <v>-0.7034</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8545</v>
+        <v>2.1671</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6103</v>
+        <v>2.1257</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2441</v>
+        <v>0.0415</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-0.3444</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.4004</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.7448</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.5425</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.4775</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. LLANO ABASCAL</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5682</v>
+        <v>1.2879</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9621</v>
+        <v>3.0163</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6062</v>
+        <v>-1.7284</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08210000000000001</v>
+        <v>-2.8223</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0592</v>
+        <v>-1.9144</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1413</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4186</v>
+        <v>1.0375</v>
       </c>
       <c r="K19" t="n">
-        <v>0.408</v>
+        <v>-1.0266</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0107</v>
+        <v>2.0641</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3366</v>
+        <v>-3.8598</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4671</v>
+        <v>-0.8878</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1306</v>
+        <v>-2.972</v>
       </c>
       <c r="P19" t="n">
         <v>0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8006</v>
+        <v>0.9075</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5434</v>
+        <v>0.2584</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2572</v>
+        <v>0.6491</v>
       </c>
       <c r="V19" t="n">
-        <v>0.315</v>
+        <v>2.8321</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.8321</v>
       </c>
       <c r="X19" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>I. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2146</v>
+        <v>1.1519</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9184</v>
+        <v>0.5703</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7038</v>
+        <v>0.5815</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8223</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9144</v>
+        <v>-0.0592</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9078000000000001</v>
+        <v>0.1413</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0375</v>
+        <v>0.4186</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0266</v>
+        <v>0.408</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0641</v>
+        <v>0.0107</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.8598</v>
+        <v>-0.3366</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8878</v>
+        <v>-0.4671</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.972</v>
+        <v>0.1306</v>
       </c>
       <c r="P20" t="n">
         <v>0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.3843</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1604</v>
+        <v>0.1517</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6737</v>
+        <v>0.2325</v>
       </c>
       <c r="V20" t="n">
-        <v>2.8321</v>
+        <v>0.315</v>
       </c>
       <c r="W20" t="n">
-        <v>2.8321</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2366</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0112</v>
+        <v>0.2825</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2478</v>
+        <v>0.3217</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0549</v>
@@ -2092,13 +2092,13 @@
         <v>1.4823</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1908</v>
+        <v>0.1769</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.383</v>
+        <v>-0.0892</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1922</v>
+        <v>0.2661</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1102</v>
+        <v>0.0611</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3876</v>
+        <v>0.5835</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4978</v>
+        <v>-0.5224</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4791</v>
@@ -2170,13 +2170,13 @@
         <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2572</v>
+        <v>0.4284</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2736</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5061</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3539</v>
+        <v>-0.6717</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0677</v>
+        <v>0.676</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4216</v>
+        <v>-1.3477</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8159999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6474</v>
+        <v>0.3295</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3246</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3228</v>
+        <v>0.3967</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. CALLE GOMEZ</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7931</v>
+        <v>-2.4917</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5922</v>
+        <v>-1.4481</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2009</v>
+        <v>-1.0436</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.6782</v>
+        <v>-2.8274</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9302</v>
+        <v>0.3076</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.748</v>
+        <v>-3.135</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2428</v>
+        <v>-0.0209</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6314</v>
+        <v>1.0561</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-1.077</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4354</v>
+        <v>-2.8065</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2989</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1366</v>
+        <v>-2.058</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1853</v>
+        <v>-2.9646</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1853</v>
+        <v>2.2234</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1149</v>
+        <v>1.0769</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1641</v>
+        <v>0.2786</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0492</v>
+        <v>0.7983</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>A. CALLE GOMEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.105</v>
+        <v>-2.7192</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8398</v>
+        <v>-1.5922</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2652</v>
+        <v>-1.127</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.8274</v>
+        <v>-2.6782</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3076</v>
+        <v>-0.9302</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.135</v>
+        <v>-1.748</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0209</v>
+        <v>-1.2428</v>
       </c>
       <c r="K25" t="n">
-        <v>1.0561</v>
+        <v>-0.6314</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.077</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.8065</v>
+        <v>-1.4354</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.2989</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.058</v>
+        <v>-1.1366</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9646</v>
+        <v>-0.1853</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2234</v>
+        <v>0.1853</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4636</v>
+        <v>-0.041</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1131</v>
+        <v>-0.1641</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5767</v>
+        <v>0.1231</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.8716</v>
+        <v>-4.8962</v>
       </c>
       <c r="E26" t="n">
         <v>-3.8042</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.0674</v>
+        <v>-1.092</v>
       </c>
       <c r="G26" t="n">
         <v>-2.1867</v>
@@ -2482,13 +2482,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0383</v>
+        <v>0.0137</v>
       </c>
       <c r="T26" t="n">
         <v>-0.2189</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2572</v>
+        <v>0.2325</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3144</v>
@@ -2515,25 +2515,25 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>20.486</v>
+        <v>20.4862</v>
       </c>
       <c r="E27" t="n">
-        <v>18.6198</v>
+        <v>18.61969999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>1.866300000000001</v>
+        <v>1.8663</v>
       </c>
       <c r="G27" t="n">
-        <v>4.747099999999999</v>
+        <v>4.747099999999994</v>
       </c>
       <c r="H27" t="n">
-        <v>7.703500000000003</v>
+        <v>7.703500000000001</v>
       </c>
       <c r="I27" t="n">
         <v>-2.956400000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>22.4626</v>
+        <v>22.46260000000001</v>
       </c>
       <c r="K27" t="n">
         <v>12.2877</v>
@@ -2560,13 +2560,13 @@
         <v>14.823</v>
       </c>
       <c r="S27" t="n">
-        <v>6.926600000000001</v>
+        <v>6.9265</v>
       </c>
       <c r="T27" t="n">
-        <v>1.2249</v>
+        <v>1.2252</v>
       </c>
       <c r="U27" t="n">
-        <v>5.7014</v>
+        <v>5.701300000000001</v>
       </c>
       <c r="V27" t="n">
         <v>8.8125</v>
